--- a/jira_export_2026-10-26.xlsx
+++ b/jira_export_2026-10-26.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>49,558 €</t>
+          <t>52,703 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>15,648 €</t>
+          <t>16,773 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>33,699 €</t>
+          <t>35,719 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>427 h</t>
+          <t>428 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0</v>
+        <v>985</v>
       </c>
       <c r="P6" s="15" t="n">
-        <v>0</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="7">
@@ -1333,10 +1333,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="P8" s="15" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>438.75</v>
+        <v>472.5</v>
       </c>
       <c r="P10" s="15" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>1040</v>
+        <v>1352</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>246.24</v>
+        <v>595.08</v>
       </c>
       <c r="P12" s="15" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>706.25</v>
       </c>
       <c r="O20" s="16" t="n">
-        <v>282.5</v>
+        <v>353.125</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>282.5</v>
+        <v>353.12</v>
       </c>
     </row>
     <row r="21">
@@ -3596,8 +3596,8 @@
       <c r="N40" s="15" t="n">
         <v>250.5</v>
       </c>
-      <c r="O40" s="16" t="n">
-        <v>0</v>
+      <c r="O40" s="15" t="n">
+        <v>250.5</v>
       </c>
       <c r="P40" s="15" t="n">
         <v>0</v>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>362.85</v>
+        <v>967.6</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
@@ -5092,11 +5092,11 @@
       <c r="N61" s="12" t="n">
         <v>1440</v>
       </c>
-      <c r="O61" s="16" t="n">
-        <v>1152</v>
+      <c r="O61" s="12" t="n">
+        <v>1512</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>53.58</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="62">
@@ -10767,7 +10767,7 @@
         <v>19</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L141" s="11" t="inlineStr">
         <is>
@@ -12841,10 +12841,10 @@
         <v>90876.166</v>
       </c>
       <c r="O176" s="18" t="n">
-        <v>49557.76700000001</v>
+        <v>52703.232</v>
       </c>
       <c r="P176" s="18" t="n">
-        <v>181.3</v>
+        <v>192.64</v>
       </c>
     </row>
   </sheetData>
@@ -14426,7 +14426,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>184.5</v>
+        <v>184.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>24</v>
@@ -14435,7 +14435,7 @@
         <v>9.83</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>218.33</v>
+        <v>218.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>38</v>
@@ -14572,16 +14572,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>477591</v>
+        <v>474446</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>202763</v>
+        <v>201276</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>274829</v>
+        <v>273169</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>218491</v>
+        <v>217436</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>13320</v>
@@ -14597,16 +14597,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>255873</v>
+        <v>254748</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>68761</v>
+        <v>68690</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>187112</v>
+        <v>186057</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>167900</v>
+        <v>166846</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -14622,13 +14622,13 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>218618</v>
+        <v>216598</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>130902</v>
+        <v>129486</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>87716</v>
+        <v>87112</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>50590</v>

--- a/jira_export_2026-10-26.xlsx
+++ b/jira_export_2026-10-26.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>52,703 €</t>
+          <t>53,747 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>35,719 €</t>
+          <t>36,763 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>428 h</t>
+          <t>433 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>301</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P176"/>
+  <dimension ref="A1:P174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4725,7 +4725,7 @@
         <v>3</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>258</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>114.67</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="57">
@@ -4822,27 +4822,27 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
@@ -4862,29 +4862,21 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34310</t>
-        </is>
-      </c>
-      <c r="M58" s="14" t="inlineStr">
-        <is>
-          <t>00171605</t>
-        </is>
-      </c>
+        <v>8.75</v>
+      </c>
+      <c r="L58" s="14" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
       <c r="N58" s="15" t="n">
-        <v>4150</v>
-      </c>
-      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4894,27 +4886,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4924,7 +4916,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -4941,14 +4933,22 @@
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="L59" s="11" t="inlineStr"/>
-      <c r="M59" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34258</t>
+        </is>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>00171361</t>
+        </is>
+      </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O59" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -4958,32 +4958,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -4993,69 +4993,69 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O60" s="16" t="n">
-        <v>0</v>
+        <v>1440</v>
+      </c>
+      <c r="O60" s="15" t="n">
+        <v>1512</v>
       </c>
       <c r="P60" s="15" t="n">
-        <v>0</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5065,49 +5065,49 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>1440</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>1512</v>
+        <v>175</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>70.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
@@ -5149,67 +5149,67 @@
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>175</v>
+        <v>775.6</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>0</v>
+        <v>692.5</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>0</v>
+        <v>230.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
@@ -5221,87 +5221,87 @@
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L63" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34201</t>
-        </is>
-      </c>
-      <c r="M63" s="11" t="inlineStr">
-        <is>
-          <t>00171162</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
       <c r="N63" s="12" t="n">
-        <v>775.6</v>
-      </c>
-      <c r="O63" s="16" t="n">
-        <v>692.5</v>
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
-        <v>230.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr"/>
-      <c r="M64" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34227</t>
+        </is>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>2026-0210095</t>
+        </is>
+      </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
-        <v>0</v>
+        <v>5388.936</v>
+      </c>
+      <c r="O64" s="16" t="n">
+        <v>4811.55</v>
       </c>
       <c r="P64" s="15" t="n">
         <v>0</v>
@@ -5310,27 +5310,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5361,19 +5361,19 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>5388.936</v>
-      </c>
-      <c r="O65" s="16" t="n">
-        <v>4811.55</v>
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
+        <v>177.5</v>
       </c>
       <c r="P65" s="12" t="n">
         <v>0</v>
@@ -5382,27 +5382,27 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5433,19 +5433,19 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15" t="n">
-        <v>177.5</v>
+        <v>1700</v>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>840</v>
       </c>
       <c r="P66" s="15" t="n">
         <v>0</v>
@@ -5454,27 +5454,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5489,64 +5489,64 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1700</v>
+        <v>1786.1</v>
       </c>
       <c r="O67" s="16" t="n">
-        <v>840</v>
+        <v>909.9</v>
       </c>
       <c r="P67" s="12" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5566,64 +5566,64 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>1786.1</v>
+        <v>170</v>
       </c>
       <c r="O68" s="16" t="n">
-        <v>909.9</v>
+        <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>303.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5633,64 +5633,64 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>170</v>
+        <v>3000</v>
       </c>
       <c r="O69" s="16" t="n">
-        <v>0</v>
+        <v>1242.9</v>
       </c>
       <c r="P69" s="12" t="n">
-        <v>0</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5717,57 +5717,57 @@
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O70" s="16" t="n">
-        <v>1242.9</v>
+        <v>484</v>
+      </c>
+      <c r="O70" s="15" t="n">
+        <v>572</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>62.15</v>
+        <v>127.11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5777,64 +5777,64 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>484</v>
-      </c>
-      <c r="O71" s="12" t="n">
-        <v>572</v>
+        <v>700</v>
+      </c>
+      <c r="O71" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
-        <v>127.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5865,16 +5865,16 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5886,32 +5886,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5921,34 +5921,34 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5958,27 +5958,27 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -5998,44 +5998,44 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0.75</v>
+        <v>8.25</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0</v>
+        <v>465.85</v>
       </c>
       <c r="P74" s="15" t="n">
-        <v>0</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6070,59 +6070,59 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>8.25</v>
+        <v>3.5</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O75" s="12" t="n">
-        <v>465.85</v>
+        <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
-        <v>56.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6149,16 +6149,16 @@
         <v>4</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
@@ -6174,32 +6174,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6214,29 +6214,29 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="12" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O77" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -6246,27 +6246,27 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6281,35 +6281,35 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K78" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="P78" s="15" t="n">
         <v>0</v>
@@ -6318,27 +6318,27 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6369,19 +6369,19 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O79" s="16" t="n">
-        <v>1062</v>
+        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
@@ -6390,27 +6390,27 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
@@ -6441,19 +6441,19 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O80" s="16" t="n">
-        <v>0</v>
+        <v>3547.9</v>
+      </c>
+      <c r="O80" s="15" t="n">
+        <v>3547.9</v>
       </c>
       <c r="P80" s="15" t="n">
         <v>0</v>
@@ -6462,27 +6462,27 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
@@ -6513,19 +6513,19 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>5634.9</v>
+        <v>500</v>
       </c>
       <c r="O81" s="16" t="n">
-        <v>2504.4</v>
+        <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
         <v>0</v>
@@ -6534,32 +6534,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6574,59 +6574,59 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="O82" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
+        <v>112.38</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>0</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -6646,69 +6646,61 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33315</t>
-        </is>
-      </c>
-      <c r="M83" s="11" t="inlineStr">
-        <is>
-          <t>00167138</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
       <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="12" t="n">
-        <v>112.38</v>
+        <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
-        <v>56.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr">
@@ -6718,21 +6710,29 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L84" s="14" t="inlineStr"/>
-      <c r="M84" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L84" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33272</t>
+        </is>
+      </c>
+      <c r="M84" s="14" t="inlineStr">
+        <is>
+          <t>00166910</t>
+        </is>
+      </c>
       <c r="N84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O84" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6742,27 +6742,27 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
@@ -6793,16 +6793,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>240</v>
+        <v>149</v>
       </c>
       <c r="O85" s="16" t="n">
         <v>0</v>
@@ -6814,32 +6814,32 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -6849,38 +6849,38 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>149</v>
+        <v>337.5</v>
       </c>
       <c r="O86" s="16" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="P86" s="15" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="87">
@@ -6937,53 +6937,53 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>337.5</v>
+        <v>320</v>
       </c>
       <c r="O87" s="16" t="n">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
-        <v>23.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -6993,35 +6993,35 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>320</v>
-      </c>
-      <c r="O88" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>1047</v>
       </c>
       <c r="P88" s="15" t="n">
         <v>0</v>
@@ -7030,32 +7030,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7065,35 +7065,35 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="12" t="n">
-        <v>1047</v>
+        <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
         <v>0</v>
@@ -7102,32 +7102,32 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
@@ -7149,22 +7149,22 @@
         <v>6</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="O90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7174,32 +7174,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7209,34 +7209,34 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="O91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7246,32 +7246,32 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
@@ -7293,22 +7293,22 @@
         <v>6</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
+        <v>680.8</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7318,12 +7318,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7353,69 +7353,69 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>680.8</v>
-      </c>
-      <c r="O93" s="16" t="n">
-        <v>0</v>
+        <v>2614.5</v>
+      </c>
+      <c r="O93" s="12" t="n">
+        <v>2614.5</v>
       </c>
       <c r="P93" s="12" t="n">
-        <v>0</v>
+        <v>871.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7425,69 +7425,69 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>2614.5</v>
+        <v>0</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>2614.5</v>
+        <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
-        <v>871.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -7509,23 +7509,23 @@
         <v>6</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O95" s="12" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="P95" s="12" t="n">
         <v>0</v>
@@ -7534,12 +7534,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
@@ -7569,35 +7569,35 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K96" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="15" t="n">
-        <v>276</v>
+        <v>220</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
         <v>0</v>
@@ -7606,27 +7606,27 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
@@ -7657,16 +7657,16 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>11278.05</v>
+        <v>450</v>
       </c>
       <c r="O97" s="16" t="n">
         <v>0</v>
@@ -7678,32 +7678,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7713,64 +7713,64 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>220</v>
+        <v>910</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>0</v>
+        <v>318.5</v>
       </c>
       <c r="P98" s="15" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
@@ -7801,16 +7801,16 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>450</v>
+        <v>4050</v>
       </c>
       <c r="O99" s="16" t="n">
         <v>0</v>
@@ -7822,32 +7822,32 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -7857,64 +7857,64 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>910</v>
+        <v>1050</v>
       </c>
       <c r="O100" s="16" t="n">
-        <v>318.5</v>
+        <v>0</v>
       </c>
       <c r="P100" s="15" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
@@ -7945,16 +7945,16 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>4050</v>
+        <v>433.5</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7966,32 +7966,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8001,34 +8001,34 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>1050</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8038,12 +8038,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8053,12 +8053,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -8073,12 +8073,12 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
@@ -8089,16 +8089,16 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>433.5</v>
+        <v>285</v>
       </c>
       <c r="O103" s="16" t="n">
         <v>0</v>
@@ -8110,12 +8110,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
@@ -8182,12 +8182,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
@@ -8233,16 +8233,16 @@
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="O105" s="16" t="n">
         <v>0</v>
@@ -8254,32 +8254,32 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -8289,34 +8289,34 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="15" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="15" t="n">
@@ -8326,12 +8326,12 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -8366,27 +8366,27 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K107" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8398,27 +8398,27 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
@@ -8449,16 +8449,16 @@
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O108" s="16" t="n">
         <v>0</v>
@@ -8470,12 +8470,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8542,12 +8542,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
@@ -8593,16 +8593,16 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="O110" s="16" t="n">
         <v>0</v>
@@ -8614,12 +8614,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
@@ -8654,27 +8654,27 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K111" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="O111" s="16" t="n">
         <v>0</v>
@@ -8686,32 +8686,32 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -8721,32 +8721,32 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="O112" s="16" t="n">
         <v>0</v>
@@ -8758,32 +8758,32 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
@@ -8793,49 +8793,49 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>140</v>
-      </c>
-      <c r="O113" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
+        <v>175</v>
       </c>
       <c r="P113" s="12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -8870,29 +8870,29 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8902,27 +8902,27 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -8942,44 +8942,44 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.5</v>
+        <v>10.25</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="12" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8989,13 +8989,11 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v/>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -9014,23 +9012,23 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9046,27 +9044,27 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
@@ -9081,34 +9079,34 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>10.25</v>
+        <v>1.9</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="O117" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9118,12 +9116,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9133,11 +9131,13 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E118" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F118" s="14" t="inlineStr">
         <is>
@@ -9151,28 +9151,28 @@
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
@@ -9239,22 +9239,22 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>275</v>
+        <v>1290</v>
       </c>
       <c r="O119" s="16" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
       <c r="P119" s="12" t="n">
-        <v>0</v>
+        <v>471.05</v>
       </c>
     </row>
     <row r="120">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
@@ -9383,33 +9383,33 @@
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>1290</v>
-      </c>
-      <c r="O121" s="16" t="n">
-        <v>895</v>
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
-        <v>471.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
@@ -9419,13 +9419,11 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E122" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v/>
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
@@ -9444,29 +9442,29 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="15" t="n">
@@ -9476,12 +9474,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9491,13 +9489,11 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v/>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
@@ -9511,34 +9507,34 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="12" t="n">
+        <v>460</v>
+      </c>
+      <c r="O123" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9548,26 +9544,28 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E124" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F124" s="14" t="inlineStr">
         <is>
@@ -9586,29 +9584,29 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="15" t="n">
@@ -9618,26 +9616,28 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
@@ -9651,34 +9651,34 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
-        <v>460</v>
-      </c>
-      <c r="O125" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
@@ -9688,12 +9688,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9703,13 +9703,11 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="n">
+        <v/>
       </c>
       <c r="F126" s="14" t="inlineStr">
         <is>
@@ -9723,65 +9721,63 @@
       </c>
       <c r="H126" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="15" t="n">
-        <v>0</v>
+        <v>3016.08</v>
+      </c>
+      <c r="O126" s="16" t="n">
+        <v>2178.28</v>
       </c>
       <c r="P126" s="15" t="n">
-        <v>0</v>
+        <v>207.46</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VILLE DE DRANCY</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v/>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
@@ -9795,28 +9791,28 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K127" s="11" t="n">
         <v>0.75</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
@@ -9832,22 +9828,22 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9865,59 +9861,59 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K128" s="14" t="n">
         <v>10.5</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O128" s="16" t="n">
-        <v>2178.28</v>
+        <v>0</v>
+      </c>
+      <c r="O128" s="15" t="n">
+        <v>2497.125</v>
       </c>
       <c r="P128" s="15" t="n">
-        <v>207.46</v>
+        <v>237.82</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9935,28 +9931,28 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
@@ -9972,12 +9968,12 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
@@ -9987,7 +9983,7 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -10010,44 +10006,44 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>2497.125</v>
+        <v>0</v>
       </c>
       <c r="P130" s="15" t="n">
-        <v>237.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -10057,7 +10053,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10080,7 +10076,7 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
@@ -10091,12 +10087,12 @@
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10127,7 +10123,7 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10161,12 +10157,12 @@
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N132" s="15" t="n">
@@ -10231,12 +10227,12 @@
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
@@ -10252,22 +10248,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22120</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD 29 ] FLUX WFS</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10280,35 +10276,27 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L134" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-30079</t>
-        </is>
-      </c>
-      <c r="M134" s="14" t="inlineStr">
-        <is>
-          <t>00152632</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L134" s="14" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
       <c r="N134" s="15" t="n">
         <v>0</v>
       </c>
@@ -10322,22 +10310,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10355,28 +10343,28 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N135" s="12" t="n">
@@ -10392,12 +10380,12 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22120</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[CD 29 ] FLUX WFS</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
@@ -10407,7 +10395,7 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10420,27 +10408,35 @@
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr"/>
-      <c r="M136" s="14" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M136" s="14" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10454,22 +10450,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10492,29 +10488,29 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N137" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O137" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P137" s="12" t="n">
@@ -10524,22 +10520,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10552,35 +10548,23 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H138" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="inlineStr"/>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L138" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M138" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L138" s="14" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
       <c r="N138" s="15" t="n">
         <v>0</v>
       </c>
@@ -10594,22 +10578,22 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10627,34 +10611,34 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M139" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N139" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O139" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="12" t="n">
@@ -10664,22 +10648,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10692,23 +10676,35 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H140" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
         <v>19</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr"/>
-      <c r="M140" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M140" s="14" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10722,22 +10718,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10760,23 +10756,23 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M141" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N141" s="12" t="n">
@@ -10792,26 +10788,28 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Marie-Maud Chiarappa</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
-        </is>
-      </c>
-      <c r="E142" s="14" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F142" s="14" t="inlineStr">
         <is>
@@ -10820,7 +10818,7 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
@@ -10830,25 +10828,17 @@
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K142" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L142" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M142" s="14" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10862,22 +10852,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10890,35 +10880,27 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27377</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="inlineStr">
-        <is>
-          <t>478048</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
@@ -10932,28 +10914,26 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E144" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>Biarritz</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="n">
+        <v/>
       </c>
       <c r="F144" s="14" t="inlineStr">
         <is>
@@ -10967,19 +10947,19 @@
       </c>
       <c r="H144" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L144" s="14" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -10996,22 +10976,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11019,36 +10999,44 @@
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L145" s="11" t="inlineStr"/>
-      <c r="M145" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L145" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N145" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O145" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P145" s="12" t="n">
@@ -11058,12 +11046,12 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
@@ -11073,7 +11061,7 @@
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11086,27 +11074,35 @@
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L146" s="14" t="inlineStr"/>
-      <c r="M146" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M146" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N146" s="15" t="n">
         <v>0</v>
       </c>
@@ -11120,22 +11116,22 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11143,44 +11139,36 @@
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M147" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr"/>
+      <c r="M147" s="11" t="inlineStr"/>
       <c r="N147" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O147" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P147" s="12" t="n">
@@ -11190,22 +11178,22 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11218,7 +11206,7 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr">
@@ -11228,25 +11216,17 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L148" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M148" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L148" s="14" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
       <c r="N148" s="15" t="n">
         <v>0</v>
       </c>
@@ -11260,22 +11240,22 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11298,14 +11278,14 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L149" s="11" t="inlineStr"/>
       <c r="M149" s="11" t="inlineStr"/>
@@ -11322,22 +11302,22 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11360,14 +11340,14 @@
       </c>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L150" s="14" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -11384,12 +11364,12 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
@@ -11399,7 +11379,7 @@
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -11417,16 +11397,16 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K151" s="11" t="n">
         <v>0.75</v>
@@ -11446,12 +11426,12 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
@@ -11461,7 +11441,7 @@
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
@@ -11474,7 +11454,7 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr">
@@ -11484,17 +11464,25 @@
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L152" s="14" t="inlineStr"/>
-      <c r="M152" s="14" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M152" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N152" s="15" t="n">
         <v>0</v>
       </c>
@@ -11508,22 +11496,22 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -11539,21 +11527,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H153" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H153" s="11" t="inlineStr"/>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>0.75</v>
+        <v>3.75</v>
       </c>
       <c r="L153" s="11" t="inlineStr"/>
       <c r="M153" s="11" t="inlineStr"/>
@@ -11570,22 +11554,22 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E154" s="14" t="n">
@@ -11598,33 +11582,33 @@
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>1.25</v>
+        <v>8.5</v>
       </c>
       <c r="L154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M154" s="14" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N154" s="15" t="n">
@@ -11640,22 +11624,22 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[CD06] Littéralis expert</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -11668,23 +11652,31 @@
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L155" s="11" t="inlineStr"/>
-      <c r="M155" s="11" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L155" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M155" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N155" s="12" t="n">
         <v>0</v>
       </c>
@@ -11698,26 +11690,24 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C156" s="14" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr"/>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
-        </is>
-      </c>
-      <c r="E156" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F156" s="14" t="inlineStr">
         <is>
@@ -11736,25 +11726,17 @@
       </c>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L156" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M156" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="L156" s="14" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
       <c r="N156" s="15" t="n">
         <v>0</v>
       </c>
@@ -11768,27 +11750,21 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
-        </is>
-      </c>
-      <c r="C157" s="11" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
-        </is>
-      </c>
-      <c r="E157" s="11" t="n">
-        <v/>
-      </c>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr"/>
       <c r="F157" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11796,31 +11772,23 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L157" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M157" s="11" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L157" s="11" t="inlineStr"/>
+      <c r="M157" s="11" t="inlineStr"/>
       <c r="N157" s="12" t="n">
         <v>0</v>
       </c>
@@ -11834,58 +11802,46 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
-      <c r="D158" s="14" t="inlineStr">
-        <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E158" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
-      <c r="F158" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+      <c r="D158" s="14" t="inlineStr"/>
+      <c r="E158" s="14" t="inlineStr"/>
+      <c r="F158" s="14" t="inlineStr"/>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H158" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H158" s="14" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K158" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L158" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L158" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
       <c r="M158" s="14" t="inlineStr"/>
       <c r="N158" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O158" s="15" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P158" s="15" t="n">
         <v>0</v>
@@ -11894,18 +11850,18 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr"/>
@@ -11922,11 +11878,11 @@
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159" s="11" t="n">
         <v>0.25</v>
@@ -11946,46 +11902,50 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1357</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
-      <c r="D160" s="14" t="inlineStr"/>
+      <c r="D160" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE BARRAUX</t>
+        </is>
+      </c>
       <c r="E160" s="14" t="inlineStr"/>
-      <c r="F160" s="14" t="inlineStr"/>
+      <c r="F160" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-36143</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L160" s="14" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O160" s="15" t="n">
-        <v>210.8</v>
+        <v>0</v>
       </c>
       <c r="P160" s="15" t="n">
         <v>0</v>
@@ -11994,18 +11954,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -12016,48 +11976,56 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K161" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L161" s="11" t="inlineStr"/>
-      <c r="M161" s="11" t="inlineStr"/>
+      <c r="L161" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M161" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N161" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" s="12" t="n">
-        <v>0</v>
+        <v>450</v>
+      </c>
+      <c r="O161" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="P161" s="12" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12074,11 +12042,11 @@
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K162" s="14" t="n">
         <v>0.25</v>
@@ -12098,18 +12066,18 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12126,50 +12094,50 @@
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35312</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M163" s="11" t="inlineStr">
         <is>
-          <t>00177354</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N163" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O163" s="16" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="O163" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P163" s="12" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12186,14 +12154,14 @@
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L164" s="14" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -12210,18 +12178,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12232,31 +12200,23 @@
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L165" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M165" s="11" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L165" s="11" t="inlineStr"/>
+      <c r="M165" s="11" t="inlineStr"/>
       <c r="N165" s="12" t="n">
         <v>0</v>
       </c>
@@ -12270,18 +12230,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12298,14 +12258,14 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K166" s="14" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="L166" s="14" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -12322,18 +12282,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12344,23 +12304,31 @@
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L167" s="11" t="inlineStr"/>
-      <c r="M167" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L167" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M167" s="11" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N167" s="12" t="n">
         <v>0</v>
       </c>
@@ -12374,18 +12342,18 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12396,23 +12364,31 @@
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K168" s="14" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L168" s="14" t="inlineStr"/>
-      <c r="M168" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L168" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M168" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N168" s="15" t="n">
         <v>0</v>
       </c>
@@ -12426,18 +12402,18 @@
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr"/>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr"/>
@@ -12448,13 +12424,13 @@
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr"/>
       <c r="I169" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J169" s="11" t="n">
@@ -12463,16 +12439,8 @@
       <c r="K169" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L169" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M169" s="11" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+      <c r="L169" s="11" t="inlineStr"/>
+      <c r="M169" s="11" t="inlineStr"/>
       <c r="N169" s="12" t="n">
         <v>0</v>
       </c>
@@ -12486,18 +12454,18 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C170" s="14" t="inlineStr"/>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr"/>
@@ -12514,23 +12482,23 @@
       <c r="H170" s="14" t="inlineStr"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J170" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K170" s="14" t="n">
         <v>0.5</v>
       </c>
       <c r="L170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-30236</t>
         </is>
       </c>
       <c r="M170" s="14" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00152992</t>
         </is>
       </c>
       <c r="N170" s="15" t="n">
@@ -12546,18 +12514,18 @@
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr"/>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr"/>
@@ -12574,11 +12542,11 @@
       <c r="H171" s="11" t="inlineStr"/>
       <c r="I171" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J171" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K171" s="11" t="n">
         <v>0.25</v>
@@ -12598,18 +12566,18 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>PSC-1119</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B172" s="14" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C172" s="14" t="inlineStr"/>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr"/>
@@ -12626,23 +12594,23 @@
       <c r="H172" s="14" t="inlineStr"/>
       <c r="I172" s="14" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J172" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K172" s="14" t="n">
         <v>0.5</v>
       </c>
       <c r="L172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30236</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M172" s="14" t="inlineStr">
         <is>
-          <t>00152992</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N172" s="15" t="n">
@@ -12658,18 +12626,18 @@
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>PSC-1060</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr"/>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr"/>
@@ -12686,14 +12654,14 @@
       <c r="H173" s="11" t="inlineStr"/>
       <c r="I173" s="11" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J173" s="11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K173" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L173" s="11" t="inlineStr"/>
       <c r="M173" s="11" t="inlineStr"/>
@@ -12708,143 +12676,31 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="13" t="inlineStr">
-        <is>
-          <t>PSC-1047</t>
-        </is>
-      </c>
-      <c r="B174" s="14" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C174" s="14" t="inlineStr"/>
-      <c r="D174" s="14" t="inlineStr">
-        <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="E174" s="14" t="inlineStr"/>
-      <c r="F174" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G174" s="14" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H174" s="14" t="inlineStr"/>
-      <c r="I174" s="14" t="inlineStr">
-        <is>
-          <t>04/11/2025</t>
-        </is>
-      </c>
-      <c r="J174" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K174" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L174" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M174" s="14" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
-      <c r="N174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O174" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="10" t="inlineStr">
-        <is>
-          <t>PSC-850</t>
-        </is>
-      </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="C175" s="11" t="inlineStr"/>
-      <c r="D175" s="11" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="E175" s="11" t="inlineStr"/>
-      <c r="F175" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G175" s="11" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H175" s="11" t="inlineStr"/>
-      <c r="I175" s="11" t="inlineStr">
-        <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="J175" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="K175" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L175" s="11" t="inlineStr"/>
-      <c r="M175" s="11" t="inlineStr"/>
-      <c r="N175" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O175" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P175" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="17" t="inlineStr">
+      <c r="A174" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B176" s="17" t="inlineStr"/>
-      <c r="C176" s="17" t="inlineStr"/>
-      <c r="D176" s="17" t="inlineStr"/>
-      <c r="E176" s="17" t="inlineStr"/>
-      <c r="F176" s="17" t="inlineStr"/>
-      <c r="G176" s="17" t="inlineStr"/>
-      <c r="H176" s="17" t="inlineStr"/>
-      <c r="I176" s="17" t="inlineStr"/>
-      <c r="J176" s="17" t="inlineStr"/>
-      <c r="K176" s="17" t="inlineStr"/>
-      <c r="L176" s="17" t="inlineStr"/>
-      <c r="M176" s="17" t="inlineStr"/>
-      <c r="N176" s="18" t="n">
-        <v>90876.166</v>
-      </c>
-      <c r="O176" s="18" t="n">
-        <v>52703.232</v>
-      </c>
-      <c r="P176" s="18" t="n">
-        <v>192.64</v>
+      <c r="B174" s="17" t="inlineStr"/>
+      <c r="C174" s="17" t="inlineStr"/>
+      <c r="D174" s="17" t="inlineStr"/>
+      <c r="E174" s="17" t="inlineStr"/>
+      <c r="F174" s="17" t="inlineStr"/>
+      <c r="G174" s="17" t="inlineStr"/>
+      <c r="H174" s="17" t="inlineStr"/>
+      <c r="I174" s="17" t="inlineStr"/>
+      <c r="J174" s="17" t="inlineStr"/>
+      <c r="K174" s="17" t="inlineStr"/>
+      <c r="L174" s="17" t="inlineStr"/>
+      <c r="M174" s="17" t="inlineStr"/>
+      <c r="N174" s="18" t="n">
+        <v>73361.11600000001</v>
+      </c>
+      <c r="O174" s="18" t="n">
+        <v>53746.732</v>
+      </c>
+      <c r="P174" s="18" t="n">
+        <v>195.02</v>
       </c>
     </row>
   </sheetData>
@@ -13019,8 +12875,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId171"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14426,16 +14280,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>184.75</v>
+        <v>185.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>24</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>9.83</v>
+        <v>10.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>218.58</v>
+        <v>219.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>38</v>
@@ -14445,7 +14299,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -14462,10 +14316,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -14475,7 +14329,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.9%</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14341,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>111.83</v>
+        <v>115.33</v>
       </c>
     </row>
   </sheetData>
@@ -14572,16 +14426,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>474446</v>
+        <v>473402</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>201276</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>273169</v>
+        <v>272126</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>217436</v>
+        <v>216392</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>13320</v>
@@ -14622,16 +14476,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>216598</v>
+        <v>215554</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>129486</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>87112</v>
+        <v>86068</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>50590</v>
+        <v>49547</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>4145</v>

--- a/jira_export_2026-10-26.xlsx
+++ b/jira_export_2026-10-26.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>447 h</t>
+          <t>453 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -5717,7 +5717,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>20</v>
+        <v>21.25</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>1242.9</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>62.15</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="71">
@@ -6933,7 +6933,7 @@
         <v>5</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>112.5</v>
       </c>
       <c r="P87" s="12" t="n">
-        <v>23.08</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="88">
@@ -7005,7 +7005,7 @@
         <v>5</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>160</v>
       </c>
       <c r="P88" s="15" t="n">
-        <v>32.82</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="89">
@@ -12772,7 +12772,7 @@
         <v>56849.857</v>
       </c>
       <c r="P175" s="18" t="n">
-        <v>199.76</v>
+        <v>198.55</v>
       </c>
     </row>
   </sheetData>
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>188.5</v>
+        <v>190.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>24</v>
@@ -14362,7 +14362,7 @@
         <v>10.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>222.58</v>
+        <v>224.33</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>39</v>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>119.33</v>
+        <v>123.83</v>
       </c>
     </row>
   </sheetData>
